--- a/artfynd/A 2991-2026 artfynd.xlsx
+++ b/artfynd/A 2991-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1765497</v>
+        <v>6939609</v>
       </c>
       <c r="B2" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93231</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5966</v>
+        <v>1968</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>772294.226930587</v>
+        <v>772192</v>
       </c>
       <c r="R2" t="n">
-        <v>7083732.225469809</v>
+        <v>7083179</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2012-10-12</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-09-13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2012-10-12</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-09-13</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,7 +759,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>sandtallskog</t>
+          <t>sandhed</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -792,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6939609</v>
+        <v>121202828</v>
       </c>
       <c r="B3" t="n">
-        <v>90638</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93231</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,25 +797,28 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bankera violascens</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Långviksskatan, Vb</t>
+          <t>Långviksskatan, Täftelandet, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>772192.2750441842</v>
+        <v>772204</v>
       </c>
       <c r="R3" t="n">
-        <v>7083178.940127277</v>
+        <v>7083191</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,22 +845,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2013-09-13</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2013-09-13</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-15</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>sannolikt den ännu obeskrivna arten knuten till sandmiljöer</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -886,13 +864,9 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>sandhed</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -912,12 +886,7 @@
         <v>6952770</v>
       </c>
       <c r="B4" t="n">
-        <v>90639</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93222</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -934,12 +903,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,10 +918,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>772300.9309170423</v>
+        <v>772301</v>
       </c>
       <c r="R4" t="n">
-        <v>7083742.139916209</v>
+        <v>7083742</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,19 +951,9 @@
           <t>2013-09-20</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2013-09-20</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,16 +988,11 @@
         <v>6952771</v>
       </c>
       <c r="B5" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1066,10 +1020,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>772303.6437607144</v>
+        <v>772304</v>
       </c>
       <c r="R5" t="n">
-        <v>7083921.019255178</v>
+        <v>7083921</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,19 +1053,9 @@
           <t>2013-09-20</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2013-09-20</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,37 +1087,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>6952767</v>
+        <v>112277864</v>
       </c>
       <c r="B6" t="n">
-        <v>88748</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93201</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5977</v>
+        <v>4365</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sandrottryffel</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scleroderma septentrionale</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Jeppson</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1183,10 +1122,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>772305.9189705</v>
+        <v>772310</v>
       </c>
       <c r="R6" t="n">
-        <v>7083495.032612268</v>
+        <v>7083785</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,22 +1152,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2013-09-20</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2013-09-20</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1239,71 +1168,61 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>sandbarrskog, sandig vägkant</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Ruaridh Hägglund</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Ruaridh Hägglund</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>88447109</v>
+        <v>121202830</v>
       </c>
       <c r="B7" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92348</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5966</v>
+        <v>5420</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Långviksskatan, Vb</t>
+          <t>Långviksskatan, Täftelandet, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>772207.7327160556</v>
+        <v>772200</v>
       </c>
       <c r="R7" t="n">
-        <v>7083170.058425168</v>
+        <v>7083295</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1330,22 +1249,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2020-10-07</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2020-10-07</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1372,15 +1281,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>88447110</v>
+        <v>96081747</v>
       </c>
       <c r="B8" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1388,34 +1292,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5966</v>
+        <v>5964</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Långviksskatan, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>772205.1266735622</v>
+        <v>772218</v>
       </c>
       <c r="R8" t="n">
-        <v>7083189.833687718</v>
+        <v>7083354</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1442,22 +1349,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2020-10-07</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2020-10-07</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-12</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1466,6 +1363,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1484,37 +1382,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>92171780</v>
+        <v>1765497</v>
       </c>
       <c r="B9" t="n">
-        <v>77532</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6434</v>
+        <v>5966</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1524,13 +1417,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>772296.1786636934</v>
+        <v>772294</v>
       </c>
       <c r="R9" t="n">
-        <v>7083479.076237362</v>
+        <v>7083732</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1554,22 +1447,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2021-04-03</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-10-12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2021-04-03</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-10-12</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1581,9 +1464,9 @@
       <c r="AG9" t="b">
         <v>0</v>
       </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>tall</t>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>sandtallskog</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1594,44 +1477,39 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Andreas Garpebring, Åsa Gustafsson</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>92171779</v>
+        <v>88447109</v>
       </c>
       <c r="B10" t="n">
-        <v>77532</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6434</v>
+        <v>5966</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1641,10 +1519,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>772318.0001989251</v>
+        <v>772208</v>
       </c>
       <c r="R10" t="n">
-        <v>7083658.295952526</v>
+        <v>7083170</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1671,22 +1549,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2021-04-03</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-10-07</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2021-04-03</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-10-07</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1697,11 +1565,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1711,44 +1574,39 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Andreas Garpebring, Åsa Gustafsson</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>92171778</v>
+        <v>88447110</v>
       </c>
       <c r="B11" t="n">
-        <v>77532</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6434</v>
+        <v>5966</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1758,10 +1616,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>772308.3140832931</v>
+        <v>772205</v>
       </c>
       <c r="R11" t="n">
-        <v>7083703.229086749</v>
+        <v>7083190</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1788,22 +1646,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2021-04-03</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-10-07</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2021-04-03</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-10-07</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1814,11 +1662,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1828,44 +1671,39 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Andreas Garpebring, Åsa Gustafsson</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>92171777</v>
+        <v>96392331</v>
       </c>
       <c r="B12" t="n">
-        <v>77532</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6434</v>
+        <v>5966</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1875,10 +1713,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>772311.461028375</v>
+        <v>772322</v>
       </c>
       <c r="R12" t="n">
-        <v>7083851.48595121</v>
+        <v>7083633</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1905,22 +1743,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2021-04-03</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2021-04-03</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1931,11 +1759,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1945,60 +1768,52 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Andreas Garpebring, Åsa Gustafsson</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>96081747</v>
+        <v>112277869</v>
       </c>
       <c r="B13" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5964</v>
+        <v>5966</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Långviksskatan, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>772218.0227865101</v>
+        <v>772320</v>
       </c>
       <c r="R13" t="n">
-        <v>7083354.070586852</v>
+        <v>7083627</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2025,22 +1840,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2021-09-12</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-23</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2021-09-12</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-23</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2049,34 +1854,28 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Ruaridh Hägglund</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Ruaridh Hägglund</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>96392331</v>
+        <v>120791100</v>
       </c>
       <c r="B14" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2104,14 +1903,14 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Långviksskatan, Vb</t>
+          <t>Långviksskatan, Täftelandet, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>772322.3914629837</v>
+        <v>772221</v>
       </c>
       <c r="R14" t="n">
-        <v>7083633.345628526</v>
+        <v>7083392</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2138,22 +1937,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-31</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-31</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2180,50 +1969,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>96392329</v>
+        <v>120791102</v>
       </c>
       <c r="B15" t="n">
-        <v>88019</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6276</v>
+        <v>5966</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Långviksskatan, Vb</t>
+          <t>Långviksskatan, Täftelandet, Vb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>772310.2763143699</v>
+        <v>772306</v>
       </c>
       <c r="R15" t="n">
-        <v>7083875.379787224</v>
+        <v>7083889</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2250,22 +2034,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-31</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-31</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2292,37 +2066,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>112277864</v>
+        <v>6952767</v>
       </c>
       <c r="B16" t="n">
-        <v>90859</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91224</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4365</v>
+        <v>5977</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Sandrottryffel</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Scleroderma septentrionale</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>Jeppson</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2332,10 +2101,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>772311</v>
+        <v>772306</v>
       </c>
       <c r="R16" t="n">
-        <v>7083785</v>
+        <v>7083495</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2362,12 +2131,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2023-09-23</t>
+          <t>2013-09-20</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2023-09-23</t>
+          <t>2013-09-20</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2378,53 +2147,53 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>sandbarrskog, sandig vägkant</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Ruaridh Hägglund</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ruaridh Hägglund</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>112277869</v>
+        <v>96392329</v>
       </c>
       <c r="B17" t="n">
-        <v>90878</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90691</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5966</v>
+        <v>6276</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2434,10 +2203,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>772319</v>
+        <v>772310</v>
       </c>
       <c r="R17" t="n">
-        <v>7083626</v>
+        <v>7083875</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2464,12 +2233,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2023-09-23</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2023-09-23</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2484,74 +2253,57 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Ruaridh Hägglund</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Ruaridh Hägglund</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>116888509</v>
+        <v>92171777</v>
       </c>
       <c r="B18" t="n">
-        <v>56483</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79351</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102612</v>
+        <v>6434</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Långvikskatan, vid vägen, Täftelandet, Vb</t>
+          <t>Långviksskatan, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>772207</v>
+        <v>772311</v>
       </c>
       <c r="R18" t="n">
-        <v>7083215</v>
+        <v>7083851</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2578,12 +2330,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-05-12</t>
+          <t>2021-04-03</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-05-12</t>
+          <t>2021-04-03</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2594,31 +2346,31 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Maud Tyboni</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Maud Tyboni</t>
+          <t>Andreas Garpebring, Åsa Gustafsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>116888500</v>
+        <v>92171778</v>
       </c>
       <c r="B19" t="n">
-        <v>57275</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79351</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2626,46 +2378,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>102119</v>
+        <v>6434</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Göktyta</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Jynx torquilla</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Långvikskatan, vid vägen, Täftelandet, Vb</t>
+          <t>Långviksskatan, Vb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>772207</v>
+        <v>772308</v>
       </c>
       <c r="R19" t="n">
-        <v>7083215</v>
+        <v>7083703</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2692,12 +2432,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-05-12</t>
+          <t>2021-04-03</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-05-12</t>
+          <t>2021-04-03</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2708,66 +2448,66 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Maud Tyboni</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Maud Tyboni</t>
+          <t>Andreas Garpebring, Åsa Gustafsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120791102</v>
+        <v>92171779</v>
       </c>
       <c r="B20" t="n">
-        <v>91998</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79351</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5966</v>
+        <v>6434</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Långviksskatan, Täftelandet, Vb</t>
+          <t>Långviksskatan, Vb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>772306</v>
+        <v>772318</v>
       </c>
       <c r="R20" t="n">
-        <v>7083889</v>
+        <v>7083658</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2794,12 +2534,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-10-31</t>
+          <t>2021-04-03</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-10-31</t>
+          <t>2021-04-03</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2810,6 +2550,11 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2819,57 +2564,52 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Andreas Garpebring, Åsa Gustafsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120791100</v>
+        <v>92171780</v>
       </c>
       <c r="B21" t="n">
-        <v>91998</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79351</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5966</v>
+        <v>6434</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Långviksskatan, Täftelandet, Vb</t>
+          <t>Långviksskatan, Vb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>772221</v>
+        <v>772296</v>
       </c>
       <c r="R21" t="n">
-        <v>7083392</v>
+        <v>7083479</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2896,12 +2636,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-10-31</t>
+          <t>2021-04-03</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-10-31</t>
+          <t>2021-04-03</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2912,6 +2652,11 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2921,60 +2666,67 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Andreas Garpebring, Åsa Gustafsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121202830</v>
+        <v>132972786</v>
       </c>
       <c r="B22" t="n">
-        <v>91125</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57124</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5420</v>
+        <v>100006</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Stjärtand</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Anas acuta</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Långviksskatan, Täftelandet, Vb</t>
+          <t>Långviksskatan, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>772200</v>
+        <v>772184</v>
       </c>
       <c r="R22" t="n">
-        <v>7083295</v>
+        <v>7083273</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2998,12 +2750,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3018,27 +2780,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Selma Skoglund</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Selma Skoglund</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121202828</v>
+        <v>132972787</v>
       </c>
       <c r="B23" t="n">
-        <v>92027</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57527</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3046,40 +2803,49 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1968</v>
+        <v>100134</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Skräntärna</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Hydroprogne caspia</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+          <t>(Pallas, 1770)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Långviksskatan, Täftelandet, Vb</t>
+          <t>Långviksskatan, Vb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>772204</v>
+        <v>772184</v>
       </c>
       <c r="R23" t="n">
-        <v>7083191</v>
+        <v>7083273</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3103,17 +2869,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>sannolikt den ännu obeskrivna arten knuten till sandmiljöer</t>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3122,22 +2893,575 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
+          <t>Selma Skoglund</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Selma Skoglund</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>116888500</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57942</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>102119</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Göktyta</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Jynx torquilla</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Långvikskatan, vid vägen, Täftelandet, Vb</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>772207</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7083215</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-05-12</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-05-12</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Maud Tyboni</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Maud Tyboni</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>116888509</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57132</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Långvikskatan, vid vägen, Täftelandet, Vb</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>772207</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7083215</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-05-12</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-05-12</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Maud Tyboni</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Maud Tyboni</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>132972759</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57032</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>102930</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Gravand</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Tadorna tadorna</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Långviksskatan, Vb</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>772184</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7083273</v>
+      </c>
+      <c r="S26" t="n">
+        <v>29</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Selma Skoglund</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Selma Skoglund</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>132972760</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57317</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>102950</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Strandskata</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Haematopus ostralegus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Långviksskatan, Vb</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>772184</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7083273</v>
+      </c>
+      <c r="S27" t="n">
+        <v>29</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Selma Skoglund</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Selma Skoglund</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>92171775</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79350</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Långviksskatan, Vb</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>772306</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7083891</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2021-04-03</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2021-04-03</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
           <t>Andreas Garpebring</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>Andreas Garpebring</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr"/>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring, Åsa Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 2991-2026 artfynd.xlsx
+++ b/artfynd/A 2991-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AY29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2911,27 +2911,27 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>116888500</v>
+        <v>134706853</v>
       </c>
       <c r="B24" t="n">
-        <v>57942</v>
+        <v>57776</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>102119</v>
+        <v>102118</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Göktyta</t>
+          <t>Nattskärra</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Jynx torquilla</t>
+          <t>Caprimulgus europaeus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2939,11 +2939,7 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
@@ -2954,17 +2950,17 @@
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Långvikskatan, vid vägen, Täftelandet, Vb</t>
+          <t>Hällskär, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>772207</v>
+        <v>772517</v>
       </c>
       <c r="R24" t="n">
-        <v>7083215</v>
+        <v>7083950</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2988,12 +2984,27 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-05-12</t>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>02:22</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-05-12</t>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>03:00</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ljudfil finns</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3008,44 +3019,44 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Maud Tyboni</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Maud Tyboni</t>
+          <t>Elin Kannerby, Alva Danielsson, Isac Enetjärn, Sara Ranesson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>116888509</v>
+        <v>116888500</v>
       </c>
       <c r="B25" t="n">
-        <v>57132</v>
+        <v>57942</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>102612</v>
+        <v>102119</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Göktyta</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Jynx torquilla</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3057,7 +3068,7 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3129,27 +3140,27 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132972759</v>
+        <v>116888509</v>
       </c>
       <c r="B26" t="n">
-        <v>57032</v>
+        <v>57132</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>102930</v>
+        <v>102612</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gravand</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tadorna tadorna</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3164,21 +3175,25 @@
       </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Långviksskatan, Vb</t>
+          <t>Långvikskatan, vid vägen, Täftelandet, Vb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>772184</v>
+        <v>772207</v>
       </c>
       <c r="R26" t="n">
-        <v>7083273</v>
+        <v>7083215</v>
       </c>
       <c r="S26" t="n">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3202,22 +3217,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>14:02</t>
+          <t>2024-05-12</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>14:02</t>
+          <t>2024-05-12</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3232,22 +3237,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Selma Skoglund</t>
+          <t>Maud Tyboni</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Selma Skoglund</t>
+          <t>Maud Tyboni</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132972760</v>
+        <v>132972759</v>
       </c>
       <c r="B27" t="n">
-        <v>57317</v>
+        <v>57032</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3255,35 +3260,31 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>102950</v>
+        <v>102930</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Strandskata</t>
+          <t>Gravand</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Haematopus ostralegus</t>
+          <t>Tadorna tadorna</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>rastande</t>
-        </is>
-      </c>
+      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3326,7 +3327,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3336,7 +3337,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3363,10 +3364,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>92171775</v>
+        <v>132972760</v>
       </c>
       <c r="B28" t="n">
-        <v>79350</v>
+        <v>57317</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3374,37 +3375,49 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>260591</v>
+        <v>102950</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Strandskata</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Haematopus ostralegus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Långviksskatan, Vb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>772306</v>
+        <v>772184</v>
       </c>
       <c r="R28" t="n">
-        <v>7083891</v>
+        <v>7083273</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3428,12 +3441,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2021-04-03</t>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2021-04-03</t>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3444,24 +3467,121 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
+          <t>Selma Skoglund</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Selma Skoglund</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>92171775</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79350</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Långviksskatan, Vb</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>772306</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7083891</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2021-04-03</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2021-04-03</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
           <t>Andreas Garpebring</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
+      <c r="AX29" t="inlineStr">
         <is>
           <t>Andreas Garpebring, Åsa Gustafsson</t>
         </is>
       </c>
-      <c r="AY28" t="inlineStr"/>
+      <c r="AY29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 2991-2026 artfynd.xlsx
+++ b/artfynd/A 2991-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AY40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3249,10 +3249,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132972759</v>
+        <v>134753040</v>
       </c>
       <c r="B27" t="n">
-        <v>57032</v>
+        <v>57816</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3260,16 +3260,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>102930</v>
+        <v>102621</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gravand</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tadorna tadorna</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3277,28 +3277,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>bo, hörda ungar</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Långviksskatan, Vb</t>
+          <t>Hällskär, Vb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>772184</v>
+        <v>772009</v>
       </c>
       <c r="R27" t="n">
-        <v>7083273</v>
+        <v>7083727</v>
       </c>
       <c r="S27" t="n">
-        <v>29</v>
+        <v>68</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3322,22 +3322,27 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>02:18</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>02:18</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ljudfil finns</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3352,22 +3357,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Selma Skoglund</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Selma Skoglund</t>
+          <t>Elin Kannerby, Alva Danielsson, Isac Enetjärn, Sara Ranesson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132972760</v>
+        <v>132972759</v>
       </c>
       <c r="B28" t="n">
-        <v>57317</v>
+        <v>57032</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3375,35 +3380,31 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>102950</v>
+        <v>102930</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Strandskata</t>
+          <t>Gravand</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Haematopus ostralegus</t>
+          <t>Tadorna tadorna</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>rastande</t>
-        </is>
-      </c>
+      <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3446,7 +3447,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3456,7 +3457,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3483,10 +3484,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>92171775</v>
+        <v>132972760</v>
       </c>
       <c r="B29" t="n">
-        <v>79350</v>
+        <v>57317</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3494,37 +3495,49 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>260591</v>
+        <v>102950</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Strandskata</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Haematopus ostralegus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Långviksskatan, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>772306</v>
+        <v>772184</v>
       </c>
       <c r="R29" t="n">
-        <v>7083891</v>
+        <v>7083273</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3548,12 +3561,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2021-04-03</t>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2021-04-03</t>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3564,24 +3587,1291 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
+          <t>Selma Skoglund</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Selma Skoglund</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>134753029</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57824</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>102975</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Hornuggla</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Asio otus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>bo, hörda ungar</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Hällskär, Vb</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>772106</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7083469</v>
+      </c>
+      <c r="S30" t="n">
+        <v>11</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>01:18</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>01:18</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ljudfil finns</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson, Sara Ranesson, Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>134753039</v>
+      </c>
+      <c r="B31" t="n">
+        <v>57824</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>102975</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Hornuggla</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Asio otus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>bo, hörda ungar</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Hällskär, Vb</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>772009</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7083727</v>
+      </c>
+      <c r="S31" t="n">
+        <v>68</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>01:53</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>01:53</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ljudfil finns</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson, Isac Enetjärn, Sara Ranesson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>134753012</v>
+      </c>
+      <c r="B32" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Hällskär, Vb</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>772477</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7083702</v>
+      </c>
+      <c r="S32" t="n">
+        <v>66</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>02:21</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>02:21</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson, Sara Ranesson, Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>134753042</v>
+      </c>
+      <c r="B33" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Hällskär, Vb</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>772009</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7083727</v>
+      </c>
+      <c r="S33" t="n">
+        <v>68</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>04:33</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>04:33</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson, Isac Enetjärn, Sara Ranesson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>134753056</v>
+      </c>
+      <c r="B34" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Hällskär, Vb</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>772517</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7083950</v>
+      </c>
+      <c r="S34" t="n">
+        <v>25</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>05:30</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>05:30</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson, Isac Enetjärn, Sara Ranesson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>134753008</v>
+      </c>
+      <c r="B35" t="n">
+        <v>58131</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Hällskär, Vb</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>772477</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7083702</v>
+      </c>
+      <c r="S35" t="n">
+        <v>66</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson, Sara Ranesson, Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>134753031</v>
+      </c>
+      <c r="B36" t="n">
+        <v>58131</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Hällskär, Vb</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>772009</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7083727</v>
+      </c>
+      <c r="S36" t="n">
+        <v>68</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson, Isac Enetjärn, Sara Ranesson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>134799310</v>
+      </c>
+      <c r="B37" t="n">
+        <v>58131</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Hällskär, Vb</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>772517</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7083950</v>
+      </c>
+      <c r="S37" t="n">
+        <v>25</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson, Isac Enetjärn, Sara Ranesson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>134753007</v>
+      </c>
+      <c r="B38" t="n">
+        <v>58678</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>103056</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Videsparv</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Emberiza rustica</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Pallas, 1776</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Hällskär, Vb</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>772477</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7083702</v>
+      </c>
+      <c r="S38" t="n">
+        <v>66</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>02:22</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>02:22</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ljudfil finns</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson, Sara Ranesson, Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>134753048</v>
+      </c>
+      <c r="B39" t="n">
+        <v>58678</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>103056</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Videsparv</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Emberiza rustica</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Pallas, 1776</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Hällskär, Vb</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>772517</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7083950</v>
+      </c>
+      <c r="S39" t="n">
+        <v>25</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ljudfil finns</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson, Isac Enetjärn, Sara Ranesson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>92171775</v>
+      </c>
+      <c r="B40" t="n">
+        <v>79350</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Långviksskatan, Vb</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>772306</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7083891</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2021-04-03</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2021-04-03</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
           <t>Andreas Garpebring</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
+      <c r="AX40" t="inlineStr">
         <is>
           <t>Andreas Garpebring, Åsa Gustafsson</t>
         </is>
       </c>
-      <c r="AY29" t="inlineStr"/>
+      <c r="AY40" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 2991-2026 artfynd.xlsx
+++ b/artfynd/A 2991-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY56"/>
+  <dimension ref="A1:AZ56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -787,6 +792,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134834628</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134706861</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1001,6 +1016,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134706862</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1108,6 +1128,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134706869</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1210,6 +1235,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6939609</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1316,6 +1346,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121202828</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1418,6 +1453,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6952770</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1520,6 +1560,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6952771</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1617,6 +1662,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112277864</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1714,6 +1764,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121202830</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1821,6 +1876,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134706866</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1934,6 +1994,11 @@
       <c r="AY13" t="inlineStr">
         <is>
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134834625</t>
         </is>
       </c>
     </row>
@@ -2037,6 +2102,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96081747</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2139,6 +2209,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1765497</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2236,6 +2311,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88447109</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2333,6 +2413,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88447110</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2430,6 +2515,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96392331</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2527,6 +2617,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112277869</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2624,6 +2719,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120791100</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2721,6 +2821,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120791102</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2823,6 +2928,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6952767</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2920,6 +3030,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96392329</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3022,6 +3137,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92171777</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3124,6 +3244,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92171778</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3226,6 +3351,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92171779</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3328,6 +3458,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92171780</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3443,6 +3578,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134834626</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3562,6 +3702,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132972786</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3674,6 +3819,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134706856</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3794,6 +3944,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134706835</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3914,6 +4069,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134706836</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4034,6 +4194,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134706858</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4154,6 +4319,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134706863</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4274,6 +4444,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134706867</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4394,6 +4569,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134706868</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4514,6 +4694,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134706870</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4634,6 +4819,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134834627</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4753,6 +4943,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132972787</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4873,6 +5068,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134706853</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4982,6 +5182,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116888500</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5091,6 +5296,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116888509</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5211,6 +5421,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134753040</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5326,6 +5541,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132972759</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5445,6 +5665,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132972760</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5565,6 +5790,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134753029</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5685,6 +5915,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134753039</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5800,6 +6035,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134753012</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5915,6 +6155,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134753042</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6030,6 +6275,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134753056</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6145,6 +6395,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134753008</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6260,6 +6515,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134753031</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6375,6 +6635,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134799310</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6495,6 +6760,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134753007</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6615,6 +6885,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134753048</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6717,8 +6992,70 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92171775</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 2991-2026 artfynd.xlsx
+++ b/artfynd/A 2991-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ56"/>
+  <dimension ref="A1:AZ58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6283,56 +6283,60 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>134753008</v>
+        <v>136028633</v>
       </c>
       <c r="B51" t="n">
-        <v>58131</v>
+        <v>58141</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>103023</v>
+        <v>103021</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Hällskär, Vb</t>
+          <t>Långvikskatan, vid vägen, Täftelandet, Vb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>772477</v>
+        <v>772207</v>
       </c>
       <c r="R51" t="n">
-        <v>7083702</v>
+        <v>7083215</v>
       </c>
       <c r="S51" t="n">
-        <v>66</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6356,22 +6360,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>05:00</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>05:00</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6386,24 +6380,24 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Maud Tyboni</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Isac Enetjärn</t>
+          <t>Maud Tyboni</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134753008</t>
+          <t>https://artportalen.se/Sighting/136028633</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>134753031</v>
+        <v>134753008</v>
       </c>
       <c r="B52" t="n">
         <v>58131</v>
@@ -6436,7 +6430,7 @@
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
@@ -6446,13 +6440,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>772009</v>
+        <v>772477</v>
       </c>
       <c r="R52" t="n">
-        <v>7083727</v>
+        <v>7083702</v>
       </c>
       <c r="S52" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6476,22 +6470,22 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>05:00</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>05:00</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6517,13 +6511,13 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134753031</t>
+          <t>https://artportalen.se/Sighting/134753008</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>134799310</v>
+        <v>134753031</v>
       </c>
       <c r="B53" t="n">
         <v>58131</v>
@@ -6556,7 +6550,7 @@
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N53" t="inlineStr"/>
@@ -6566,13 +6560,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>772517</v>
+        <v>772009</v>
       </c>
       <c r="R53" t="n">
-        <v>7083950</v>
+        <v>7083727</v>
       </c>
       <c r="S53" t="n">
-        <v>25</v>
+        <v>68</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6596,22 +6590,22 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:25</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:25</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6637,16 +6631,16 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134799310</t>
+          <t>https://artportalen.se/Sighting/134753031</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>134753007</v>
+        <v>134799310</v>
       </c>
       <c r="B54" t="n">
-        <v>58678</v>
+        <v>58131</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6654,21 +6648,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>103056</v>
+        <v>103023</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Videsparv</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Emberiza rustica</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Pallas, 1776</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6676,7 +6670,7 @@
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N54" t="inlineStr"/>
@@ -6686,13 +6680,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>772477</v>
+        <v>772517</v>
       </c>
       <c r="R54" t="n">
-        <v>7083702</v>
+        <v>7083950</v>
       </c>
       <c r="S54" t="n">
-        <v>66</v>
+        <v>25</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6716,27 +6710,22 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>02:22</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>02:22</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Ljudfil finns</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6762,16 +6751,16 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134753007</t>
+          <t>https://artportalen.se/Sighting/134799310</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>134753048</v>
+        <v>136028635</v>
       </c>
       <c r="B55" t="n">
-        <v>58678</v>
+        <v>58601</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6779,45 +6768,49 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>103056</v>
+        <v>103041</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Videsparv</t>
+          <t>Bergfink</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Emberiza rustica</t>
+          <t>Fringilla montifringilla</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Pallas, 1776</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Hällskär, Vb</t>
+          <t>Långvikskatan, vid vägen, Täftelandet, Vb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>772517</v>
+        <v>772207</v>
       </c>
       <c r="R55" t="n">
-        <v>7083950</v>
+        <v>7083215</v>
       </c>
       <c r="S55" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6841,27 +6834,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>06:00</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>06:00</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Ljudfil finns</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6876,65 +6854,73 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Maud Tyboni</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Isac Enetjärn</t>
+          <t>Maud Tyboni</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134753048</t>
+          <t>https://artportalen.se/Sighting/136028635</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>92171775</v>
+        <v>134753007</v>
       </c>
       <c r="B56" t="n">
-        <v>79350</v>
+        <v>58678</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>260591</v>
+        <v>103056</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Videsparv</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Emberiza rustica</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>Pallas, 1776</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Långviksskatan, Vb</t>
+          <t>Hällskär, Vb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>772306</v>
+        <v>772477</v>
       </c>
       <c r="R56" t="n">
-        <v>7083891</v>
+        <v>7083702</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6958,12 +6944,27 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2021-04-03</t>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>02:22</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2021-04-03</t>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>02:22</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ljudfil finns</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6974,25 +6975,252 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Andreas Garpebring, Åsa Gustafsson</t>
+          <t>Elin Kannerby, Alva Danielsson, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134753007</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>134753048</v>
+      </c>
+      <c r="B57" t="n">
+        <v>58678</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>103056</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Videsparv</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Emberiza rustica</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Pallas, 1776</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Hällskär, Vb</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>772517</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7083950</v>
+      </c>
+      <c r="S57" t="n">
+        <v>25</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ljudfil finns</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson, Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134753048</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>92171775</v>
+      </c>
+      <c r="B58" t="n">
+        <v>79350</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Långviksskatan, Vb</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>772306</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7083891</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2021-04-03</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2021-04-03</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring, Åsa Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/92171775</t>
         </is>
@@ -7055,6 +7283,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 2991-2026 artfynd.xlsx
+++ b/artfynd/A 2991-2026 artfynd.xlsx
@@ -6286,7 +6286,7 @@
         <v>136028633</v>
       </c>
       <c r="B51" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6760,7 +6760,7 @@
         <v>136028635</v>
       </c>
       <c r="B55" t="n">
-        <v>58601</v>
+        <v>58603</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 2991-2026 artfynd.xlsx
+++ b/artfynd/A 2991-2026 artfynd.xlsx
@@ -6286,7 +6286,7 @@
         <v>136028633</v>
       </c>
       <c r="B51" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6760,7 +6760,7 @@
         <v>136028635</v>
       </c>
       <c r="B55" t="n">
-        <v>58603</v>
+        <v>58604</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 2991-2026 artfynd.xlsx
+++ b/artfynd/A 2991-2026 artfynd.xlsx
@@ -6286,7 +6286,7 @@
         <v>136028633</v>
       </c>
       <c r="B51" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6760,7 +6760,7 @@
         <v>136028635</v>
       </c>
       <c r="B55" t="n">
-        <v>58604</v>
+        <v>58608</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 2991-2026 artfynd.xlsx
+++ b/artfynd/A 2991-2026 artfynd.xlsx
@@ -6286,7 +6286,7 @@
         <v>136028633</v>
       </c>
       <c r="B51" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6760,7 +6760,7 @@
         <v>136028635</v>
       </c>
       <c r="B55" t="n">
-        <v>58608</v>
+        <v>58609</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 2991-2026 artfynd.xlsx
+++ b/artfynd/A 2991-2026 artfynd.xlsx
@@ -6286,7 +6286,7 @@
         <v>136028633</v>
       </c>
       <c r="B51" t="n">
-        <v>58149</v>
+        <v>58154</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6760,7 +6760,7 @@
         <v>136028635</v>
       </c>
       <c r="B55" t="n">
-        <v>58609</v>
+        <v>58614</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 2991-2026 artfynd.xlsx
+++ b/artfynd/A 2991-2026 artfynd.xlsx
@@ -6286,7 +6286,7 @@
         <v>136028633</v>
       </c>
       <c r="B51" t="n">
-        <v>58154</v>
+        <v>58167</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6760,7 +6760,7 @@
         <v>136028635</v>
       </c>
       <c r="B55" t="n">
-        <v>58614</v>
+        <v>58627</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
